--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DE7AFD-8855-40B8-80E8-8815DD180A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B628A55-4DBD-406E-A00C-3F300279FE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="90">
   <si>
     <t>Year</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>Road show - TBD</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
 </sst>
 </file>
@@ -993,8 +990,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:J90" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A2:J90" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:J89" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A2:J89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="21"/>
@@ -1292,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C514591A-F47A-421D-8C5F-2D1DE3B987E2}">
-  <dimension ref="A2:J90"/>
+  <dimension ref="A2:J89"/>
   <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2850,15 +2847,15 @@
       </c>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>15</v>
@@ -2867,40 +2864,25 @@
         <v>17</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J65" s="18"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A66" s="10">
-        <v>2027</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H65" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2909,7 +2891,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2918,7 +2900,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2927,7 +2909,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2936,7 +2918,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2945,7 +2927,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2954,7 +2936,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2963,7 +2945,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2972,7 +2954,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2981,7 +2963,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2990,7 +2972,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2999,7 +2981,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3008,7 +2990,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3017,7 +2999,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3106,15 +3088,6 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B628A55-4DBD-406E-A00C-3F300279FE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE0D6EE-063E-4B04-B869-967A1FC4D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="93">
   <si>
     <t>Year</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>Road show - TBD</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Upcomming</t>
   </si>
 </sst>
 </file>
@@ -438,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -491,14 +500,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -727,25 +733,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="AUMOVIO Office"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -990,19 +977,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:J89" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A2:J89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{64F28885-5723-4016-A635-CFF656BD6E8F}" name="Date" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{97870B60-4225-4FCB-8859-43B51E3D1AA1}" name="Category" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{F05E5941-12DB-4C96-A801-3623F4A74C54}" name="Role" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{2552D41C-D8E3-49B0-9415-CC8E91A50898}" name="Content" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{96CAE995-30DC-420B-85E3-2C6431DF9E5C}" name="Video" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{E55FEAF9-7EBC-4B17-8448-2E7ADADC6148}" name="Article" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{B0A32CDB-8196-4E4B-8ADF-09F397A28011}" name="Remark 1" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{D16368D4-D007-4B6D-A91C-2872EFFD09FF}" name="Remark 2" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I89" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
+  <autoFilter ref="A2:I89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{64F28885-5723-4016-A635-CFF656BD6E8F}" name="Date" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{97870B60-4225-4FCB-8859-43B51E3D1AA1}" name="Category" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{F05E5941-12DB-4C96-A801-3623F4A74C54}" name="Role" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{2552D41C-D8E3-49B0-9415-CC8E91A50898}" name="Content" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{96CAE995-30DC-420B-85E3-2C6431DF9E5C}" name="Video" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{E55FEAF9-7EBC-4B17-8448-2E7ADADC6148}" name="Article" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{B0A32CDB-8196-4E4B-8ADF-09F397A28011}" name="Status" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1289,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C514591A-F47A-421D-8C5F-2D1DE3B987E2}">
-  <dimension ref="A2:J89"/>
+  <dimension ref="A2:I89"/>
   <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -1299,11 +1285,11 @@
     <col min="5" max="5" width="24.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="56.81640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.54296875" style="2" customWidth="1"/>
-    <col min="8" max="10" width="17.54296875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.81640625" style="1"/>
+    <col min="8" max="9" width="17.54296875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1329,13 +1315,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>2026</v>
       </c>
@@ -1355,10 +1338,11 @@
         <v>13</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2026</v>
       </c>
@@ -1381,10 +1365,11 @@
         <v>16</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I4" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>2026</v>
       </c>
@@ -1407,10 +1392,11 @@
         <v>16</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I5" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>2026</v>
       </c>
@@ -1430,10 +1416,11 @@
         <v>19</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I6" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>2026</v>
       </c>
@@ -1456,10 +1443,11 @@
         <v>16</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I7" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>2026</v>
       </c>
@@ -1481,10 +1469,11 @@
       <c r="H8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I8" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>2026</v>
       </c>
@@ -1509,10 +1498,11 @@
       <c r="H9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I9" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>2026</v>
       </c>
@@ -1532,10 +1522,11 @@
         <v>23</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I10" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2026</v>
       </c>
@@ -1557,10 +1548,11 @@
       <c r="H11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I11" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>2026</v>
       </c>
@@ -1582,10 +1574,11 @@
       <c r="H12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I12" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>2026</v>
       </c>
@@ -1607,10 +1600,11 @@
       <c r="H13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I13" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>2026</v>
       </c>
@@ -1630,10 +1624,11 @@
         <v>29</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I14" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>2026</v>
       </c>
@@ -1655,8 +1650,11 @@
       <c r="H15" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I15" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>2026</v>
       </c>
@@ -1676,10 +1674,11 @@
         <v>30</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>2026</v>
       </c>
@@ -1704,10 +1703,11 @@
       <c r="H17" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I17" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>2026</v>
       </c>
@@ -1727,10 +1727,11 @@
         <v>31</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I18" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>2026</v>
       </c>
@@ -1753,8 +1754,11 @@
         <v>16</v>
       </c>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I19" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>2026</v>
       </c>
@@ -1777,10 +1781,11 @@
         <v>16</v>
       </c>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I20" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>2026</v>
       </c>
@@ -1803,10 +1808,11 @@
       <c r="H21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+      <c r="I21" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>2026</v>
       </c>
@@ -1826,8 +1832,11 @@
         <v>36</v>
       </c>
       <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I22" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>2026</v>
       </c>
@@ -1847,10 +1856,11 @@
         <v>37</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I23" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>2026</v>
       </c>
@@ -1875,8 +1885,11 @@
       <c r="H24" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I24" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>2026</v>
       </c>
@@ -1899,10 +1912,11 @@
       <c r="H25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I25" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>2026</v>
       </c>
@@ -1922,8 +1936,11 @@
         <v>40</v>
       </c>
       <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I26" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>2026</v>
       </c>
@@ -1948,10 +1965,11 @@
       <c r="H27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I27" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>2026</v>
       </c>
@@ -1974,10 +1992,11 @@
         <v>16</v>
       </c>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I28" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>2026</v>
       </c>
@@ -2000,10 +2019,11 @@
         <v>16</v>
       </c>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I29" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>2026</v>
       </c>
@@ -2026,10 +2046,11 @@
         <v>16</v>
       </c>
       <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I30" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>2026</v>
       </c>
@@ -2051,10 +2072,11 @@
       <c r="H31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I31" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>2026</v>
       </c>
@@ -2076,10 +2098,11 @@
       <c r="H32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I32" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>2026</v>
       </c>
@@ -2104,9 +2127,11 @@
       <c r="H33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I33" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>2026</v>
       </c>
@@ -2126,8 +2151,11 @@
         <v>49</v>
       </c>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I34" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>2026</v>
       </c>
@@ -2147,10 +2175,11 @@
         <v>50</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I35" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>2026</v>
       </c>
@@ -2170,8 +2199,11 @@
         <v>51</v>
       </c>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I36" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>2026</v>
       </c>
@@ -2196,8 +2228,11 @@
       <c r="H37" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I37" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>2026</v>
       </c>
@@ -2222,8 +2257,11 @@
       <c r="H38" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I38" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>2026</v>
       </c>
@@ -2246,10 +2284,11 @@
       <c r="H39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I39" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>2026</v>
       </c>
@@ -2269,9 +2308,11 @@
         <v>54</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="J40" s="18"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I40" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>2026</v>
       </c>
@@ -2291,10 +2332,11 @@
         <v>55</v>
       </c>
       <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I41" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>2026</v>
       </c>
@@ -2319,9 +2361,11 @@
       <c r="H42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I42" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>2026</v>
       </c>
@@ -2342,10 +2386,11 @@
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I43" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>2026</v>
       </c>
@@ -2368,8 +2413,11 @@
       <c r="H44" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I44" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>2026</v>
       </c>
@@ -2392,10 +2440,11 @@
       <c r="H45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+      <c r="I45" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>2026</v>
       </c>
@@ -2415,8 +2464,11 @@
         <v>59</v>
       </c>
       <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I46" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>2026</v>
       </c>
@@ -2437,10 +2489,11 @@
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I47" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>2026</v>
       </c>
@@ -2461,10 +2514,11 @@
       </c>
       <c r="G48" s="15"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I48" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>2026</v>
       </c>
@@ -2485,10 +2539,11 @@
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I49" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>2026</v>
       </c>
@@ -2509,10 +2564,11 @@
       </c>
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I50" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
         <v>2026</v>
       </c>
@@ -2533,10 +2589,11 @@
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I51" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>2026</v>
       </c>
@@ -2559,8 +2616,11 @@
       <c r="H52" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I52" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>2026</v>
       </c>
@@ -2585,8 +2645,11 @@
       <c r="H53" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I53" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="10">
         <v>2026</v>
       </c>
@@ -2609,8 +2672,11 @@
       <c r="H54" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I54" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>2026</v>
       </c>
@@ -2633,8 +2699,11 @@
       <c r="H55" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I55" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>2026</v>
       </c>
@@ -2657,8 +2726,11 @@
       <c r="H56" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I56" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>2026</v>
       </c>
@@ -2683,10 +2755,11 @@
       <c r="H57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I57" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="10">
         <v>2026</v>
       </c>
@@ -2707,10 +2780,11 @@
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I58" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="10">
         <v>2026</v>
       </c>
@@ -2735,8 +2809,11 @@
       <c r="H59" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I59" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
         <v>2026</v>
       </c>
@@ -2756,8 +2833,11 @@
         <v>71</v>
       </c>
       <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I60" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
         <v>2026</v>
       </c>
@@ -2782,8 +2862,11 @@
       <c r="H61" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I61" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
         <v>2027</v>
       </c>
@@ -2802,8 +2885,11 @@
       <c r="F62" s="13" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I62" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>2027</v>
       </c>
@@ -2825,8 +2911,11 @@
       <c r="G63" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I63" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="10">
         <v>2027</v>
       </c>
@@ -2846,8 +2935,11 @@
         <v>73</v>
       </c>
       <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I64" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
@@ -2872,8 +2964,11 @@
       <c r="H65" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I65" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2882,7 +2977,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2891,7 +2986,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2900,7 +2995,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2909,7 +3004,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2918,7 +3013,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2927,7 +3022,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2936,7 +3031,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2945,7 +3040,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2954,7 +3049,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2963,7 +3058,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2972,7 +3067,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2981,7 +3076,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2990,7 +3085,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2999,7 +3094,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3008,87 +3103,15 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-    </row>
+    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE0D6EE-063E-4B04-B869-967A1FC4D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8393438A-110A-4BBD-811E-299A92887A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="93">
   <si>
     <t>Year</t>
   </si>
@@ -316,10 +316,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Upcomming</t>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -978,7 +978,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I89" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
-  <autoFilter ref="A2:I89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
+  <autoFilter ref="A2:I89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Event"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="20"/>
@@ -1338,11 +1344,9 @@
         <v>13</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2026</v>
       </c>
@@ -1365,11 +1369,9 @@
         <v>16</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>2026</v>
       </c>
@@ -1392,9 +1394,7 @@
         <v>16</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
@@ -1416,11 +1416,9 @@
         <v>19</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>2026</v>
       </c>
@@ -1443,11 +1441,9 @@
         <v>16</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>2026</v>
       </c>
@@ -1469,11 +1465,9 @@
       <c r="H8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>2026</v>
       </c>
@@ -1498,9 +1492,7 @@
       <c r="H9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
@@ -1522,11 +1514,9 @@
         <v>23</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2026</v>
       </c>
@@ -1548,11 +1538,9 @@
       <c r="H11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>2026</v>
       </c>
@@ -1574,11 +1562,9 @@
       <c r="H12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>2026</v>
       </c>
@@ -1600,9 +1586,7 @@
       <c r="H13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
@@ -1624,11 +1608,9 @@
         <v>29</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>2026</v>
       </c>
@@ -1650,9 +1632,7 @@
       <c r="H15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
@@ -1674,11 +1654,9 @@
         <v>30</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>2026</v>
       </c>
@@ -1703,9 +1681,7 @@
       <c r="H17" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
@@ -1727,11 +1703,9 @@
         <v>31</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>2026</v>
       </c>
@@ -1754,11 +1728,9 @@
         <v>16</v>
       </c>
       <c r="H19" s="2"/>
-      <c r="I19" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>2026</v>
       </c>
@@ -1781,11 +1753,9 @@
         <v>16</v>
       </c>
       <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>2026</v>
       </c>
@@ -1808,9 +1778,7 @@
       <c r="H21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
@@ -1832,9 +1800,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="I22" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
@@ -1856,11 +1822,9 @@
         <v>37</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="I23" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>2026</v>
       </c>
@@ -1885,11 +1849,9 @@
       <c r="H24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>2026</v>
       </c>
@@ -1912,9 +1874,7 @@
       <c r="H25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
@@ -1937,10 +1897,10 @@
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>2026</v>
       </c>
@@ -1965,11 +1925,9 @@
       <c r="H27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>2026</v>
       </c>
@@ -1992,11 +1950,9 @@
         <v>16</v>
       </c>
       <c r="H28" s="2"/>
-      <c r="I28" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>2026</v>
       </c>
@@ -2019,11 +1975,9 @@
         <v>16</v>
       </c>
       <c r="H29" s="2"/>
-      <c r="I29" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>2026</v>
       </c>
@@ -2046,11 +2000,9 @@
         <v>16</v>
       </c>
       <c r="H30" s="2"/>
-      <c r="I30" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>2026</v>
       </c>
@@ -2072,11 +2024,9 @@
       <c r="H31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>2026</v>
       </c>
@@ -2098,11 +2048,9 @@
       <c r="H32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>2026</v>
       </c>
@@ -2127,9 +2075,7 @@
       <c r="H33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
@@ -2151,9 +2097,7 @@
         <v>49</v>
       </c>
       <c r="G34" s="1"/>
-      <c r="I34" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
@@ -2175,9 +2119,7 @@
         <v>50</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
@@ -2199,11 +2141,9 @@
         <v>51</v>
       </c>
       <c r="H36" s="2"/>
-      <c r="I36" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>2026</v>
       </c>
@@ -2228,11 +2168,9 @@
       <c r="H37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>2026</v>
       </c>
@@ -2257,11 +2195,9 @@
       <c r="H38" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>2026</v>
       </c>
@@ -2284,9 +2220,7 @@
       <c r="H39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I39" s="2"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
@@ -2309,7 +2243,7 @@
       </c>
       <c r="G40" s="1"/>
       <c r="I40" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -2332,11 +2266,9 @@
         <v>55</v>
       </c>
       <c r="H41" s="2"/>
-      <c r="I41" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>2026</v>
       </c>
@@ -2361,9 +2293,7 @@
       <c r="H42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
@@ -2386,11 +2316,9 @@
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15"/>
-      <c r="I43" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>2026</v>
       </c>
@@ -2413,11 +2341,9 @@
       <c r="H44" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>2026</v>
       </c>
@@ -2440,9 +2366,7 @@
       <c r="H45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
@@ -2464,9 +2388,7 @@
         <v>59</v>
       </c>
       <c r="G46" s="1"/>
-      <c r="I46" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
@@ -2489,9 +2411,7 @@
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="15"/>
-      <c r="I47" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
@@ -2514,9 +2434,7 @@
       </c>
       <c r="G48" s="15"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
@@ -2539,9 +2457,7 @@
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="15"/>
-      <c r="I49" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I49" s="2"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
@@ -2564,9 +2480,7 @@
       </c>
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
-      <c r="I50" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
@@ -2589,11 +2503,9 @@
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15"/>
-      <c r="I51" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>2026</v>
       </c>
@@ -2616,11 +2528,9 @@
       <c r="H52" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>2026</v>
       </c>
@@ -2645,11 +2555,9 @@
       <c r="H53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10">
         <v>2026</v>
       </c>
@@ -2672,11 +2580,9 @@
       <c r="H54" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>2026</v>
       </c>
@@ -2699,11 +2605,9 @@
       <c r="H55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>2026</v>
       </c>
@@ -2726,11 +2630,9 @@
       <c r="H56" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>2026</v>
       </c>
@@ -2755,9 +2657,7 @@
       <c r="H57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I57" s="2"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="10">
@@ -2780,11 +2680,9 @@
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15"/>
-      <c r="I58" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10">
         <v>2026</v>
       </c>
@@ -2809,9 +2707,7 @@
       <c r="H59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I59" s="2"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
@@ -2833,11 +2729,9 @@
         <v>71</v>
       </c>
       <c r="G60" s="1"/>
-      <c r="I60" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
         <v>2026</v>
       </c>
@@ -2862,9 +2756,7 @@
       <c r="H61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I61" s="2"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
@@ -2885,11 +2777,9 @@
       <c r="F62" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="I62" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>2027</v>
       </c>
@@ -2911,9 +2801,7 @@
       <c r="G63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="10">
@@ -2935,11 +2823,9 @@
         <v>73</v>
       </c>
       <c r="G64" s="1"/>
-      <c r="I64" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
@@ -2964,11 +2850,9 @@
       <c r="H65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2977,7 +2861,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2986,7 +2870,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2995,7 +2879,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3004,7 +2888,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3013,7 +2897,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3022,7 +2906,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3031,7 +2915,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3040,7 +2924,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3049,7 +2933,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3058,7 +2942,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3067,7 +2951,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3076,7 +2960,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3085,7 +2969,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3094,7 +2978,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3103,15 +2987,15 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="81" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="82" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="83" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="84" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="85" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="86" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="87" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8393438A-110A-4BBD-811E-299A92887A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5364B93-5AA3-4605-BAC9-40A0709A34CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="92">
   <si>
     <t>Year</t>
   </si>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>Cancelled</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -978,13 +975,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I89" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
-  <autoFilter ref="A2:I89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Event"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:I89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="20"/>
@@ -1346,7 +1337,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2026</v>
       </c>
@@ -1371,7 +1362,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>2026</v>
       </c>
@@ -1418,7 +1409,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>2026</v>
       </c>
@@ -1443,7 +1434,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>2026</v>
       </c>
@@ -1467,7 +1458,7 @@
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>2026</v>
       </c>
@@ -1516,7 +1507,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2026</v>
       </c>
@@ -1540,7 +1531,7 @@
       </c>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>2026</v>
       </c>
@@ -1564,7 +1555,7 @@
       </c>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>2026</v>
       </c>
@@ -1610,7 +1601,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>2026</v>
       </c>
@@ -1656,7 +1647,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>2026</v>
       </c>
@@ -1705,7 +1696,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>2026</v>
       </c>
@@ -1730,7 +1721,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>2026</v>
       </c>
@@ -1755,7 +1746,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>2026</v>
       </c>
@@ -1824,7 +1815,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>2026</v>
       </c>
@@ -1851,7 +1842,7 @@
       </c>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>2026</v>
       </c>
@@ -1896,11 +1887,9 @@
         <v>40</v>
       </c>
       <c r="G26" s="1"/>
-      <c r="I26" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>2026</v>
       </c>
@@ -1927,7 +1916,7 @@
       </c>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>2026</v>
       </c>
@@ -1952,7 +1941,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>2026</v>
       </c>
@@ -1977,7 +1966,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>2026</v>
       </c>
@@ -2002,7 +1991,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>2026</v>
       </c>
@@ -2026,7 +2015,7 @@
       </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>2026</v>
       </c>
@@ -2050,7 +2039,7 @@
       </c>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>2026</v>
       </c>
@@ -2143,7 +2132,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>2026</v>
       </c>
@@ -2170,7 +2159,7 @@
       </c>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>2026</v>
       </c>
@@ -2197,7 +2186,7 @@
       </c>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>2026</v>
       </c>
@@ -2268,7 +2257,7 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>2026</v>
       </c>
@@ -2318,7 +2307,7 @@
       <c r="H43" s="15"/>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>2026</v>
       </c>
@@ -2343,7 +2332,7 @@
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>2026</v>
       </c>
@@ -2505,7 +2494,7 @@
       <c r="H51" s="15"/>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>2026</v>
       </c>
@@ -2530,7 +2519,7 @@
       </c>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>2026</v>
       </c>
@@ -2557,7 +2546,7 @@
       </c>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="10">
         <v>2026</v>
       </c>
@@ -2582,7 +2571,7 @@
       </c>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>2026</v>
       </c>
@@ -2607,7 +2596,7 @@
       </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>2026</v>
       </c>
@@ -2632,7 +2621,7 @@
       </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>2026</v>
       </c>
@@ -2682,7 +2671,7 @@
       <c r="H58" s="15"/>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="10">
         <v>2026</v>
       </c>
@@ -2731,7 +2720,7 @@
       <c r="G60" s="1"/>
       <c r="I60" s="2"/>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
         <v>2026</v>
       </c>
@@ -2779,7 +2768,7 @@
       </c>
       <c r="I62" s="2"/>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>2027</v>
       </c>
@@ -2825,7 +2814,7 @@
       <c r="G64" s="1"/>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
@@ -2852,7 +2841,7 @@
       </c>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2861,7 +2850,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2870,7 +2859,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2879,7 +2868,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2888,7 +2877,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2897,7 +2886,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2906,7 +2895,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2915,7 +2904,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2924,7 +2913,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2933,7 +2922,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2942,7 +2931,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2951,7 +2940,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2960,7 +2949,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2969,7 +2958,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2978,7 +2967,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2987,15 +2976,15 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="82" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="83" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="84" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="85" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="86" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="87" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="88" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="89" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uidv9144_automotive-wan_com/Documents/Y 2026/VIO/SAM China Communication Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5364B93-5AA3-4605-BAC9-40A0709A34CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E5364B93-5AA3-4605-BAC9-40A0709A34CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C991AA6-E0DC-4409-8974-B7DF71167998}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="6" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026 old'!$A$2:$F$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$2:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$2:$F$57</definedName>
   </definedNames>
   <calcPr calcId="191028" concurrentManualCount="12"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="94">
   <si>
     <t>Year</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>Cancelled</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>delay</t>
   </si>
 </sst>
 </file>
@@ -444,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -496,6 +502,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -974,8 +983,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I89" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
-  <autoFilter ref="A2:I89" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I87" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
+  <autoFilter ref="A2:I87" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="20"/>
@@ -1272,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C514591A-F47A-421D-8C5F-2D1DE3B987E2}">
-  <dimension ref="A2:I89"/>
+  <dimension ref="A2:I87"/>
   <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2418,7 +2427,7 @@
       <c r="E48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F48" s="13" t="s">
+      <c r="F48" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G48" s="15"/>
@@ -2535,7 +2544,7 @@
       <c r="E53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -2653,7 +2662,7 @@
         <v>2026</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>66</v>
@@ -2665,10 +2674,9 @@
         <v>17</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
+        <v>71</v>
+      </c>
+      <c r="G58" s="1"/>
       <c r="I58" s="2"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2676,7 +2684,7 @@
         <v>2026</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>66</v>
@@ -2688,7 +2696,7 @@
         <v>17</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>16</v>
@@ -2700,49 +2708,45 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
-        <v>2026</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>70</v>
+        <v>2027</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G60" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="I60" s="2"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
-        <v>2026</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>70</v>
+        <v>2027</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>71</v>
+        <v>12</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I61" s="2"/>
@@ -2752,20 +2756,21 @@
         <v>2027</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G62" s="1"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2773,21 +2778,24 @@
         <v>2027</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>72</v>
+        <v>17</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="G63" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I63" s="2"/>
@@ -2796,11 +2804,11 @@
       <c r="A64" s="10">
         <v>2027</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>26</v>
+      <c r="B64" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>11</v>
@@ -2809,20 +2817,23 @@
         <v>17</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G64" s="1"/>
-      <c r="I64" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>26</v>
+      <c r="B65" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>15</v>
@@ -2831,7 +2842,7 @@
         <v>17</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
@@ -2839,7 +2850,9 @@
       <c r="H65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I65" s="2"/>
+      <c r="I65" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
@@ -2983,8 +2996,6 @@
     <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uidv9144_automotive-wan_com/Documents/Y 2026/VIO/SAM China Communication Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E5364B93-5AA3-4605-BAC9-40A0709A34CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C991AA6-E0DC-4409-8974-B7DF71167998}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{E5364B93-5AA3-4605-BAC9-40A0709A34CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{667EC899-FCF7-4BBA-869F-6D537D98DA7C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="93">
   <si>
     <t>Year</t>
   </si>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>Cancelled</t>
-  </si>
-  <si>
-    <t>Q1</t>
   </si>
   <si>
     <t>delay</t>
@@ -450,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -502,9 +499,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2427,7 +2421,7 @@
       <c r="E48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F48" s="13" t="s">
         <v>62</v>
       </c>
       <c r="G48" s="15"/>
@@ -2544,7 +2538,7 @@
       <c r="E53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="18" t="s">
+      <c r="F53" s="13" t="s">
         <v>62</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -2805,10 +2799,10 @@
         <v>2027</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>11</v>
@@ -2822,7 +2816,7 @@
       <c r="G64" s="15"/>
       <c r="H64" s="15"/>
       <c r="I64" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2830,10 +2824,10 @@
         <v>2027</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>15</v>
@@ -2851,7 +2845,7 @@
         <v>16</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
